--- a/Workbench/SDPC_B10遥测数据表.xlsx
+++ b/Workbench/SDPC_B10遥测数据表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="24765" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="遥测监控表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
   <si>
     <t>编号</t>
   </si>
@@ -59,7 +59,7 @@
     <t>0x0:状态1
 0x1:状态2
 0x2:状态3
-0x4状态4</t>
+0x4:状态4</t>
   </si>
   <si>
     <t>无</t>
@@ -87,50 +87,22 @@
     <t>b6</t>
   </si>
   <si>
-    <t>0x0:否
-0x2:是</t>
-  </si>
-  <si>
     <t>b5</t>
   </si>
   <si>
-    <t>0x0:否
-0x3:是</t>
-  </si>
-  <si>
     <t>b4</t>
   </si>
   <si>
-    <t>0x0:否
-0x4:是</t>
-  </si>
-  <si>
     <t>b3</t>
   </si>
   <si>
-    <t>0x0:否
-0x5:是</t>
-  </si>
-  <si>
     <t>b2</t>
   </si>
   <si>
-    <t>0x0:否
-0x6:是</t>
-  </si>
-  <si>
     <t>b1</t>
   </si>
   <si>
-    <t>0x0:否
-0x7:是</t>
-  </si>
-  <si>
     <t>b0</t>
-  </si>
-  <si>
-    <t>0x0:否
-0x8:是</t>
   </si>
   <si>
     <t>byte4-byte5</t>
@@ -1411,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>10</v>
@@ -1430,13 +1402,13 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>10</v>
@@ -1455,13 +1427,13 @@
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>10</v>
@@ -1480,13 +1452,13 @@
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>10</v>
@@ -1505,13 +1477,13 @@
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>10</v>
@@ -1530,13 +1502,13 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>10</v>
@@ -1555,13 +1527,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>10</v>
@@ -1577,19 +1549,19 @@
         <v>yc15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1">
         <v>16</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1602,19 +1574,19 @@
         <v>yc16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E17" s="1">
         <v>16</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1627,19 +1599,19 @@
         <v>yc17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1">
         <v>16</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1652,19 +1624,19 @@
         <v>yc18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1677,19 +1649,19 @@
         <v>yc19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1">
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1702,19 +1674,19 @@
         <v>yc20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1">
         <v>16</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1727,19 +1699,19 @@
         <v>yc21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E22" s="1">
         <v>16</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1752,19 +1724,19 @@
         <v>yc22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E23" s="1">
         <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1777,19 +1749,19 @@
         <v>yc23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1">
         <v>16</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1802,19 +1774,19 @@
         <v>yc24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E25" s="1">
         <v>16</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1827,19 +1799,19 @@
         <v>yc25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1">
         <v>16</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1852,19 +1824,19 @@
         <v>yc26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1">
         <v>16</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1877,19 +1849,19 @@
         <v>yc27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E28" s="1">
         <v>16</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1906,16 +1878,16 @@
         <v>byte30-byte33</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E29" s="1">
         <v>32</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1932,16 +1904,16 @@
         <v>byte34-byte37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E30" s="1">
         <v>32</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1958,16 +1930,16 @@
         <v>byte38-byte41</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1">
         <v>32</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1984,16 +1956,16 @@
         <v>byte42-byte45</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1">
         <v>32</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2010,16 +1982,16 @@
         <v>byte46-byte49</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E33" s="1">
         <v>32</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2036,16 +2008,16 @@
         <v>byte50-byte53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1">
         <v>32</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" ht="57" spans="1:7">
@@ -2058,10 +2030,10 @@
         <v>yc34</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E35" s="3">
         <v>4</v>
@@ -2083,19 +2055,19 @@
         <v>yc35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E36" s="3">
         <v>12</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" ht="28.5" spans="1:7">
@@ -2108,10 +2080,10 @@
         <v>yc36</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E37" s="5">
         <v>1</v>
@@ -2133,19 +2105,19 @@
         <v>yc37</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E38" s="5">
         <v>16</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2158,19 +2130,19 @@
         <v>yc38</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Workbench/SDPC_B10遥测数据表.xlsx
+++ b/Workbench/SDPC_B10遥测数据表.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="12360"/>
+    <workbookView windowWidth="22380" windowHeight="11655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测监控表" sheetId="1" r:id="rId1"/>
+    <sheet name="遥测查询标识" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="57">
   <si>
     <t>编号</t>
   </si>
@@ -190,6 +191,18 @@
   </si>
   <si>
     <t>b14-b0</t>
+  </si>
+  <si>
+    <t>遥测查询标识</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>1F</t>
+  </si>
+  <si>
+    <t>2F</t>
   </si>
 </sst>
 </file>
@@ -202,7 +215,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,138 +714,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1167,981 +1188,981 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="57" spans="1:7">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" s="2" t="str">
         <f>"yc"&amp;ROW()-1</f>
         <v>yc1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="57" spans="1:7">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <f t="shared" ref="A3:A44" si="0">ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="str">
+      <c r="B3" s="2" t="str">
         <f t="shared" ref="B3:B44" si="1">"yc"&amp;ROW()-1</f>
         <v>yc2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="57" spans="1:7">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" ht="57" spans="1:7">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="str">
+      <c r="B5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="57" spans="1:7">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="str">
+      <c r="B6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc5</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>4</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="57" spans="1:7">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="str">
+      <c r="B7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc6</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="28.5" spans="1:7">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="str">
+      <c r="B8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc7</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="28.5" spans="1:7">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="str">
+      <c r="B9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" ht="28.5" spans="1:7">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="str">
+      <c r="B10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc9</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="28.5" spans="1:7">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="str">
+      <c r="B11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc10</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" ht="28.5" spans="1:7">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="str">
+      <c r="B12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc11</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="28.5" spans="1:7">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="str">
+      <c r="B13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc12</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" ht="28.5" spans="1:7">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="str">
+      <c r="B14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc13</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" ht="28.5" spans="1:7">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="str">
+      <c r="B15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc14</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="F15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="str">
+      <c r="B16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc15</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="1">
-        <v>16</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="2">
+        <v>16</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="str">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc16</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="1">
-        <v>16</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="2">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="str">
+      <c r="B18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc17</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="1">
-        <v>16</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="E18" s="2">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="str">
+      <c r="B19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc18</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="1">
-        <v>16</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="E19" s="2">
+        <v>16</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="str">
+      <c r="B20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc19</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="1">
-        <v>16</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="E20" s="2">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="1">
+      <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="str">
+      <c r="B21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc20</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="1">
-        <v>16</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="E21" s="2">
+        <v>16</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="str">
+      <c r="B22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc21</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="1">
-        <v>16</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="2">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="str">
+      <c r="B23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc22</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="1">
-        <v>16</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="E23" s="2">
+        <v>16</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="str">
+      <c r="B24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc23</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="1">
-        <v>16</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="2">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="str">
+      <c r="B25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc24</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="1">
-        <v>16</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="E25" s="2">
+        <v>16</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="str">
+      <c r="B26" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc25</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="1">
-        <v>16</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E26" s="2">
+        <v>16</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="str">
+      <c r="B27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc26</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="1">
-        <v>16</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="2">
+        <v>16</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="str">
+      <c r="B28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc27</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="1">
-        <v>16</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="2">
+        <v>16</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="str">
+      <c r="B29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc28</v>
       </c>
-      <c r="C29" s="1" t="str">
+      <c r="C29" s="2" t="str">
         <f>"byte"&amp;(ROW()-29)*4+30&amp;"-byte"&amp;(ROW()-29)*4+33</f>
         <v>byte30-byte33</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>32</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="str">
+      <c r="B30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc29</v>
       </c>
-      <c r="C30" s="1" t="str">
+      <c r="C30" s="2" t="str">
         <f t="shared" ref="C30:C34" si="2">"byte"&amp;(ROW()-29)*4+30&amp;"-byte"&amp;(ROW()-29)*4+33</f>
         <v>byte34-byte37</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>32</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="str">
+      <c r="B31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc30</v>
       </c>
-      <c r="C31" s="1" t="str">
+      <c r="C31" s="2" t="str">
         <f t="shared" si="2"/>
         <v>byte38-byte41</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <v>32</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="str">
+      <c r="B32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc31</v>
       </c>
-      <c r="C32" s="1" t="str">
+      <c r="C32" s="2" t="str">
         <f t="shared" si="2"/>
         <v>byte42-byte45</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>32</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="str">
+      <c r="B33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc32</v>
       </c>
-      <c r="C33" s="1" t="str">
+      <c r="C33" s="2" t="str">
         <f t="shared" si="2"/>
         <v>byte46-byte49</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>32</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="str">
+      <c r="B34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>yc33</v>
       </c>
-      <c r="C34" s="1" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" si="2"/>
         <v>byte50-byte53</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>32</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" ht="57" spans="1:7">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="str">
+      <c r="B35" s="4" t="str">
         <f t="shared" si="1"/>
         <v>yc34</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="4">
         <v>4</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="str">
+      <c r="B36" s="4" t="str">
         <f t="shared" si="1"/>
         <v>yc35</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="4">
         <v>12</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" ht="28.5" spans="1:7">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="str">
+      <c r="B37" s="6" t="str">
         <f t="shared" si="1"/>
         <v>yc36</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="6">
         <v>1</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="F37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="str">
+      <c r="B38" s="6" t="str">
         <f t="shared" si="1"/>
         <v>yc37</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="5">
-        <v>16</v>
-      </c>
-      <c r="F38" s="6" t="s">
+      <c r="E38" s="6">
+        <v>16</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="str">
+      <c r="B39" s="6" t="str">
         <f t="shared" si="1"/>
         <v>yc38</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="6">
         <v>15</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2149,4 +2170,39 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>